--- a/data_extactor/batch_10_fa/batch_0095_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0095_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم ردیابی بار | Corel WordPerfect Office Suite | Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار سیستم مدیریت انبار WMS</t>
+          <t>نرم‌افزار سیستم ردیابی بار | Corel WordPerfect Office Suite | Facebook | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | پایش | استراتژی‌های یادگیری | درک مطلب | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | مدیریت و امور اداری | اداری | پرسنل و منابع انسانی | ریاضیات | آموزش و تربیت | کامپیوتر و الکترونیک | مخابرات | تولید و فرآوری | جغرافیا</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | مخابرات | تولید و فرآوری | جغرافیا</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید دور | استدلال قیاسی | دید نزدیک | هماهنگی چند عضو | توجه انتخابی | سرعت ادراکی | تشخیص گفتار | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری بستار | وضوح گفتار | تجسم فضایی | تقسیم توجه | قدرت ایستا | توجه شنیداری | قدرت تنه | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | روان بودن ایده‌ها | ثبات دست و بازو | سرعت بستار | زمان عکس‌العمل | کنترل نرخ | چالاکی دست | ادراک عمق | وسعت انعطاف‌پذیری</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی دور | استدلال قیاسی | بینایی نزدیک | هماهنگی چند عضو | توجه انتخابی | سرعت ادراکی | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | وضوح گفتار | تجسم | تقسیم توجه | قدرت ایستا | توجه شنیداری | قدرت تنه | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | روانی ایده‌ها | ثبات دست و بازو | سرعت بستار | زمان عکس‌العمل | کنترل نرخ | مهارت دستی | درک عمق | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | داخل ساختمان، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارگران | خارج از ساختمان، در معرض تمام شرایط آب و هوایی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | داخل ساختمان، با کنترل شرایط محیطی | موقعیت‌های تعارض | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در یک وسیله نقلیه روباز یا کار با تجهیزات | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان به صورت ایستاده</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط داخلی، دارای کنترل شرایط محیطی | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در یک وسیله نقلیه روباز یا کار با تجهیزات | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | نمایندگان بار و فریت | خلبانان تجاری | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران تولید و عملیات | کارگزاران ترخیص و فریت | اپراتورهای تراکتور و لیفتراک صنعتی | کارگران ساده و جابجا‌کنندگان دستی فریت، موجودی و مواد | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | بارگیران واگن‌های مخزنی، کامیون و کشتی | بازرسان حمل و نقل | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>کنترلرهای ترافیک هوایی | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | نمایندگان بار و محموله | خلبانان تجاری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول مهمانداران مسافری | سرپرستان رده اول کارگران تولید و بهره‌برداری | متصدیان حمل و نقل | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رئیس قطارها و مدیران محوطه راه‌آهن | بارگیران واگن مخزنی، کامیون و کشتی | بازرسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Corel WordPerfect Office Suite | نرم‌افزار برنامه‌ریزی کارکنان | نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Database | نرم‌افزار SAP | Sage ERP Accpac | نرم‌افزار حضور و غیاب | نرم‌افزار سیستم مدیریت انبار WMS</t>
+          <t>Corel WordPerfect Office Suite | نرم‌افزار زمان‌بندی کارکنان | نرم‌افزار کنترل موجودی | سیستم‌های مدیریت موجودی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Database | نرم‌افزار SAP | Sage ERP Accpac | نرم‌افزار حضور و غیاب | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | پایش | تفکر انتقادی | درک مطلب | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | تولید و فرآوری | مدیریت و امور اداری | مکانیک | کامپیوتر و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | آموزش و تربیت</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | مدیریت و اداره | مکانیک | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | توجه انتخابی | ترتیب‌دهی به اطلاعات | بیان کتبی | دید دور | چالاکی دست | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان کتبی | بینایی دور | مهارت دستی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و در تیم‌ها | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | مکالمات تلفنی | سلامت و ایمنی سایر کارگران | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | داخل ساختمان، با کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | موقعیت‌های تعارض | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | موقعیت‌های تعارض | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها, نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیاتی | مهندسان صنایع | مدیران تولید صنعتی | کارمندان تولید، برنامه‌ریزی و هماهنگی | هماهنگ‌کنندگان بازیافت | مونتاژکنندگان تیمی</t>
+          <t>سرپرستان جابجایی بار هواپیما | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | مهندسان صنایع | مدیران تولید صنعتی | کارمندان تولید، برنامه‌ریزی و هماهنگی | هماهنگ‌کنندگان بازیافت | مونتاژکاران تیمی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار ایمیل | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | پایگاه‌های داده عملیاتی | نرم‌افزار SAP | نرم‌افزار مرورگر وب | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>نرم‌افزار ایمیل | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | پایگاه‌های داده عملیاتی | نرم‌افزار SAP | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | پایش | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و امور اداری | اداری | آموزش و تربیت | تولید و فرآوری | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | کامپیوتر و الکترونیک | حمل و نقل</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اداری | آموزش و پرورش | تولید و فرآوری | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | حساسیت به مسئله | درک کتبی | دید نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بیان کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بیان کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و در تیم‌ها | مکالمات تلفنی | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | خارج از ساختمان، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارگران | سلامت و ایمنی سایر کارگران | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | داخل ساختمان، بدون کنترل شرایط محیطی | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران تاسیسات | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول کارگران تولید و عملیات | مدیران عمومی و عملیاتی | کارگران حذف مواد خطرناک | مدیران تولید صنعتی | متخصصان لجستیک | تحلیلگران مدیریت | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | کارگران بازیافت و احیا | جمع‌آوران زباله و مواد بازیافتی | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>مدیران تسهیلات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان رده اول کارگران تولید و بهره‌برداری | مدیران عمومی و عملیات | کارگران حذف مواد خطرناک | مدیران تولید صنعتی | لجستیسین‌ها | تحلیل‌گران مدیریت | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان مدیریت پروژه | کارگران بازیافت و احیا | جمع‌آوران زباله و مواد بازیافتی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Road GeoManager | Accellos Real Dispatch | Actsoft Comet Tracker | نرم‌افزار بارکد | نرم‌افزار بارنامه | CAPE Systems CAPE PACK | CAPE Systems TRUCKFILL | نرم‌افزار عملیات وسایل نقلیه تجاری CVO | Coptimal Logics AutoLoad Pro | Creative Systems Corporation Freight-Link System | سیستم‌های مدیریت ناوگان | نرم‌افزار دفتر کل | JDA Manugistics | نرم‌افزار بهینه‌سازی بارگیری | MagicLogic Optimization Cube-IQ | نرم‌افزار نقشه برداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Optimum Logistics LoadPlanner | نرم‌افزار اثبات تحویل POD | نرم‌افزار SAP | نرم‌افزار برنامه‌ریزی | Softtruck CargoWiz | Starre Enterprises Star Bill of Lading | Strategic Business Systems Proof of Delivery | TOPS Engineering MaxLoad Pro | UPS Logistics Technologies Roadnet Transportation Suite | نرم‌افزار سیستم مدیریت انبار WMS | نرم‌افزار مرورگر وب | XATA XATANET</t>
+          <t>Road GeoManager | Accellos Real Dispatch | Actsoft Comet Tracker | نرم‌افزار بارکد | نرم‌افزار بارنامه | CAPE Systems CAPE PACK | CAPE Systems TRUCKFILL | نرم‌افزار عملیات وسایل نقلیه تجاری CVO | Coptimal Logics AutoLoad Pro | Creative Systems Corporation Freight-Link System | سیستم‌های مدیریت ناوگان | نرم‌افزار دفتر کل | JDA Manugistics | نرم‌افزار بهینه‌سازی بارگیری | MagicLogic Optimization Cube-IQ | نرم‌افزار نقشه‌برداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Optimum Logistics LoadPlanner | نرم‌افزار اثبات تحویل POD | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | Softtruck CargoWiz | Starre Enterprises Star Bill of Lading | Strategic Business Systems Proof of Delivery | TOPS Engineering MaxLoad Pro | UPS Logistics Technologies Roadnet Transportation Suite | سیستم مدیریت انبار WMS | نرم‌افزار مرورگر وب | XATA XATANET</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | پایش | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و شخصی | ریاضیات | زبان انگلیسی | تولید و فرآوری | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | حمل و نقل | اداری | روانشناسی | آموزش و تربیت | قانون و دولت | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | تولید و فرآوری | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | رایانه و الکترونیک | حمل و نقل | اداری | روان‌شناسی | آموزش و پرورش | قانون و دولت | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | دید نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی به اطلاعات | دید دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | سهولت کار با اعداد | ابتکار | روان بودن ایده‌ها | تقسیم توجه</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توانایی عددی | اصالت | روانی ایده‌ها | تقسیم توجه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | تعیین وظایف, اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | سطح رقابت | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارگران | موقعیت‌های تعارض | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | خارج از ساختمان، در معرض تمام شرایط آب و هوایی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان به صورت پیاده‌روی یا دویدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان به صورت ایستاده | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | سطح رقابت | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن و نگهداری محوطه | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیاتی | مدیران تولید صنعتی | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | هماهنگ‌کنندگان بازیافت | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>سرپرستان جابجایی بار هواپیما | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | مدیران تولید صنعتی | رئیس قطارها و مدیران محوطه راه‌آهن | هماهنگ‌کنندگان بازیافت | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Accellos Real Dispatch | نرم‌افزار عملیات وسایل نقلیه تجاری CVO | نرم‌افزار دفتر کل | سیستم‌های مدیریت موجودی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار برنامه‌ریزی | نرم‌افزار ثبت زمان | نرم‌افزار مرورگر وب | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>Accellos Real Dispatch | نرم‌افزار عملیات وسایل نقلیه تجاری CVO | نرم‌افزار دفتر کل | سیستم‌های مدیریت موجودی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | نرم‌افزار ثبت زمان | نرم‌افزار مرورگر وب | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | پایش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل و نقل | خدمات مشتریان و شخصی | مدیریت و امور اداری | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و تربیت | جغرافیا</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | مدیریت و اداره | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | چالاکی انگشتان | چالاکی دست | دید دور | حفظ کردن | روان بودن ایده‌ها | بیان کتبی | ابتکار</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره به چهره با افراد و در تیم‌ها | نزدیکی فیزیکی | صرف زمان به صورت ایستاده | صرف زمان به صورت پیاده‌روی یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | داخل ساختمان، با کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | ایمیل | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیاتی | متخصصان منابع انسانی | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | متخصصان منابع انسانی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل و نقل | نرم‌افزار سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP | Microsoft PowerPoint</t>
+          <t>نرم‌افزار مدیریت ناوگان | نرم‌افزار مدیریت حمل و نقل | سیستم مدیریت انبار WMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | Microsoft Outlook | سیستم برنامه‌ریزی منابع سازمانی ERP | Microsoft PowerPoint</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | پایش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل و نقل | مدیریت و امور اداری | ایمنی و امنیت عمومی | خدمات مشتریان و شخصی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و تربیت | قانون و دولت | کامپیوتر و الکترونیک</t>
+          <t>حمل و نقل | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | قانون و دولت | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | ابتکار | توجه انتخابی | تقسیم توجه | تجسم فضایی | حفظ کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره به چهره با افراد و در تیم‌ها | داخل ساختمان، با کنترل شرایط محیطی | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | پیامد خطا | سلامت و ایمنی سایر کارگران | داخل ساختمان، بدون کنترل شرایط محیطی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | پیامد خطا | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول جابجایی بار هواپیما | هماهنگ‌کنندگان بازیافت | مدیران حمل و نقل، انبارداری و توزیع | متخصصان لجستیک | تحلیلگران لجستیک | مدیران زنجیره تامین | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | نمایندگان بار و فریت | کارگزاران ترخیص و فریت | بازرسان حمل و نقل | متخصصان عملیات فرودگاه | رانندگان کامیون‌های سنگین و تریلی | رانندگان اتوبوس، درون‌شهری و بین‌شهری | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | مدیران عمومی و عملیاتی | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان بهداشت و ایمنی شغلی</t>
+          <t>سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان جابجایی بار هواپیما | هماهنگ‌کنندگان بازیافت | مدیران حمل‌ونقل، انبارداری و توزیع | لجستیسین‌ها | تحلیلگران لجستیک | مدیران زنجیره تأمین | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | نمایندگان بار و محموله | متصدیان حمل و نقل | بازرسان حمل‌ونقل | متخصصان عملیات فرودگاه | رانندگان کامیون‌های سنگین و تریلی | رانندگان اتوبوس، ترانزیت و بین‌شهری | رئیس قطارها و مدیران محوطه راه‌آهن | مدیران عمومی و عملیات | کارمندان تولید، برنامه‌ریزی و هماهنگی | متخصصان بهداشت و ایمنی شغلی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AeroPlanner | AirSmith FlightPrompt | Airline Pilots Daily Aviation Log PPC | CoPilot Flight Planning &amp; E6B | Document Object Model DOM Scripting | پایگاه‌های داده الکترونیکی اطلاعات هواپیما | IFT-Pro | MJICCS PilotLog | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Navzilla | Nimblefeet Technologies Captain's Keeper | Notam Development Group Airport Insight | Pilot Navigator Software Load Balance | Polaris Microsystems AeroLog Pro | Polaris Microsystems CharterLog | R | RMS Technology Flitesoft | SBS International Maestro Suite | Skylog Services Skylog Pro | doXstor Flight Level Logbook</t>
+          <t>AeroPlanner | AirSmith FlightPrompt | Airline Pilots Daily Aviation Log PPC | CoPilot Flight Planning &amp; E6B | اسکریپت‌نویسی مدل شیء سند DOM | پایگاه‌های داده الکترونیکی اطلاعات هواگرد | IFT-Pro | MJICCS PilotLog | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Navzilla | Nimblefeet Technologies Captain's Keeper | Notam Development Group Airport Insight | Pilot Navigator Software Load Balance | Polaris Microsystems AeroLog Pro | Polaris Microsystems CharterLog | R | RMS Technology Flitesoft | SBS International Maestro Suite | Skylog Services Skylog Pro | doXstor Flight Level Logbook</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | پایش | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | جغرافیا | مکانیک | ریاضیات | کامپیوتر و الکترونیک | فیزیک | قانون و دولت | خدمات مشتریان و شخصی | مدیریت و امور اداری</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | جغرافیا | مکانیک | ریاضیات | رایانه و الکترونیک | فیزیک | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>جهت‌گیری پاسخ | حساسیت به مسئله | دقت کنترل | دید دور | دید نزدیک | زمان عکس‌العمل | کنترل نرخ | ادراک عمق | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری بستار | جهت‌گیری فضایی | توجه انتخابی | تقسیم توجه | ثبات دست و بازو | هماهنگی چند عضو | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | دید محیطی | وضوح گفتار | حساسیت شنیداری | تشخیص گفتار | تشخیص رنگ‌های بصری | حساسیت به درخشندگی شدید | چالاکی دست | تجسم فضایی | سرعت بستار | دید شبانه | سهولت کار با اعداد | توجه شنیداری | چالاکی انگشتان | حفظ کردن | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها</t>
+          <t>جهت‌گیری پاسخ | حساسیت به مسئله | دقت کنترل | بینایی دور | بینایی نزدیک | زمان عکس‌العمل | کنترل نرخ | درک عمق | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری بستار | جهت‌گیری فضایی | توجه انتخابی | تقسیم توجه | ثبات دست و بازو | هماهنگی چند عضو | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی محیطی | وضوح گفتار | حساسیت شنوایی | تشخیص گفتار | تشخیص رنگ بصری | حساسیت به درخشندگی شدید | مهارت دستی | تجسم | سرعت بستار | بینایی در شب | توانایی عددی | توجه شنیداری | مهارت انگشتان | حفظ کردن | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | صرف زمان به صورت نشسته | گفتگوهای چهره به چهره با افراد و در تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | سطح رقابت | نزدیکی فیزیکی | ایمیل | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارگران | داخل ساختمان، با کنترل شرایط محیطی | سخنرانی عمومی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتفاعات بالا | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | میزان خودکارسازی | قرار گرفتن در معرض تشعشعات | قرار گرفتن در معرض آلاینده‌ها</t>
+          <t>اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | سطح رقابت | نزدیکی فیزیکی | ایمیل | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتفاعات بالا | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | میزان خودکارسازی | قرار گرفتن در معرض تابش | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنیسین‌ها و کمک‌کارشناسان مهندسی هوافضا و عملیات | مهندسان هوافضا | کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | مکانیک‌ها و تکنسین‌های خدمات هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | بازرسان هوانوردی | تکنسین‌های اویونیک | کاپیتان‌ها، افسران و خلبانان شناورهای دریایی | خلبانان تجاری | سرپرستان خط اول مهمانداران مسافری | مهمانداران هواپیما | رانندگان لوکوموتیو | اپراتورهای قایق موتوری | ترمزبانان، ماموران سیگنال و سوزنبانان راه‌آهن و کمک‌رانندگان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | بازرسان حمل و نقل</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | مکانیک‌ها و تکنسین‌های خدمات هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | بازرسان هوانوردی | تکنسین‌های هوانوردی | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | خلبانان تجاری | سرپرستان خط اول مهمانداران مسافری | مهمانداران هواپیما | مهندسان لوکوموتیو | اپراتورهای قایق موتوری | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | ملوانان و روغن‌کاران دریایی | مهندسان کشتی | بازرسان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Creative Cloud software | AeroPlanner | نقشه های هوانوردی | AirSmith FlightPrompt | Airdata | Airline Pilots Daily Aviation Log PPC | ArduPilot Mission Planner | نرم‌افزار کالیبراسیون | CloudCompare | ESRI Site Scan for ArcGIS | پایگاه‌های داده الکترونیکی اطلاعات هواپیما | FLIR Thermal Studio Suite | نرم‌افزار شبیه‌سازی پرواز | Kitty Hawk | LP360 | Litchi | MJICCS PilotLog | نرم‌افزار Microsoft Office | Navzilla | Nimblefeet Technologies Captain's Keeper | Notam Development Group Airport Insight | OpenDroneMap | Pilot Navigator Software Load Balance | Pix4D Pix4Dcapture | Pix4D Pix4Dmapper | Polaris Microsystems AeroLog Pro | Polaris Microsystems CharterLog | RMS Technology Flitesoft | SBS International Maestro Suite | Skylog Services Skylog Pro | زبان نشانه‌گذاری تعمیم‌یافته استاندارد SGML | UgCS | doXstor Flight Level Logbook</t>
+          <t>نرم‌افزار Adobe Creative Cloud | AeroPlanner | نقشه‌های هوانوردی | AirSmith FlightPrompt | Airdata | Airline Pilots Daily Aviation Log PPC | ArduPilot Mission Planner | نرم‌افزار کالیبراسیون | CloudCompare | ESRI Site Scan for ArcGIS | پایگاه‌های داده الکترونیکی اطلاعات هواگرد | FLIR Thermal Studio Suite | نرم‌افزار شبیه‌سازی پرواز | Kitty Hawk | LP360 | Litchi | MJICCS PilotLog | نرم‌افزار Microsoft Office | Navzilla | Nimblefeet Technologies Captain's Keeper | Notam Development Group Airport Insight | OpenDroneMap | Pilot Navigator Software Load Balance | Pix4D Pix4Dcapture | Pix4D Pix4Dmapper | Polaris Microsystems AeroLog Pro | Polaris Microsystems CharterLog | RMS Technology Flitesoft | SBS International Maestro Suite | Skylog Services Skylog Pro | زبان نشانه‌گذاری تعمیم‌یافته استاندارد SGML | UgCS | doXstor Flight Level Logbook</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | کامپیوتر و الکترونیک | فیزیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | رایانه و الکترونیک | فیزیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | سرعت ادراکی | دقت کنترل | دید نزدیک | جهت‌گیری پاسخ | زمان عکس‌العمل | دید دور | ادراک عمق | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | هماهنگی چند عضو | کنترل نرخ | جهت‌گیری فضایی | درک کتبی | تشخیص گفتار | وضوح گفتار | تقسیم توجه | انعطاف‌پذیری بستار | چالاکی دست | بیان کتبی | ثبات دست و بازو | تجسم فضایی | توجه شنیداری | حساسیت شنیداری | حساسیت به درخشندگی شدید | سرعت بستار | انعطاف‌پذیری دسته‌بندی | ابتکار | روان بودن ایده‌ها | دید محیطی | تشخیص رنگ‌های بصری</t>
+          <t>حساسیت به مسئله | سرعت ادراکی | دقت کنترل | بینایی نزدیک | جهت‌گیری پاسخ | زمان عکس‌العمل | بینایی دور | درک عمق | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | کنترل نرخ | جهت‌گیری فضایی | درک کتبی | تشخیص گفتار | وضوح گفتار | تقسیم توجه | انعطاف‌پذیری بستار | مهارت دستی | بیان کتبی | ثبات دست و بازو | تجسم | توجه شنیداری | حساسیت شنوایی | حساسیت به درخشندگی شدید | سرعت بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | بینایی محیطی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | گفتگوهای چهره به چهره با افراد و در تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | صرف زمان به صورت نشسته | مکالمات تلفنی | نزدیکی فیزیکی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامد خطا | فشار زمانی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | خارج از ساختمان، در معرض تمام شرایط آب و هوایی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | داخل ساختمان، با کنترل شرایط محیطی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | مکالمات تلفنی | نزدیکی فیزیکی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | فشار زمانی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنیسین‌ها و کمک‌کارشناسان مهندسی هوافضا و عملیات | کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | مکانیک‌ها و تکنسین‌های خدمات هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | بازرسان هوانوردی | تکنسین‌های اویونیک | اپراتورهای دوربین، تلویزیون، ویدیو و فیلم | کاپیتان‌ها، افسران و خلبانان شناورهای دریایی | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | مهمانداران هواپیما | رانندگان کامیون‌های سنگین و تریلی | رانندگان لوکوموتیو | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | تکنسین‌های سنجش از دور | مهندسان کشتی | بازرسان حمل و نقل</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | مکانیک‌ها و تکنسین‌های خدمات هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | بازرسان هوانوردی | تکنسین‌های هوانوردی | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | ناخدایان، افسران دوم و راهنمایان شناورهای دریایی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مهمانداران هواپیما | رانندگان کامیون‌های سنگین و تریلی | مهندسان لوکوموتیو | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | تکنسین‌های سنجش از دور | مهندسان کشتی | بازرسان حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | پایش | یادگیری فعال | درک مطلب | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و تربیت | خدمات مشتریان و شخصی | جغرافیا | مخابرات | ریاضیات</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و پرورش | خدمات مشتری و شخصی | جغرافیا | مخابرات | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | استدلال قیاسی | انعطاف‌پذیری بستار | سرعت بستار | استدلال استقرایی | سرعت ادراکی | تقسیم توجه | دید نزدیک | دید دور | وضوح گفتار | ترتیب‌دهی به اطلاعات | تشخیص گفتار | درک کتبی | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | تجسم فضایی | ابتکار | روان بودن ایده‌ها | بیان کتبی | استدلال ریاضی | تشخیص رنگ‌های بصری | حفظ کردن | سهولت کار با اعداد</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | استدلال قیاسی | انعطاف‌پذیری بستار | سرعت بستار | استدلال استقرایی | سرعت ادراکی | تقسیم توجه | بینایی نزدیک | بینایی دور | وضوح گفتار | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک کتبی | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | تجسم | اصالت | روانی ایده‌ها | بیان کتبی | استدلال ریاضی | تشخیص رنگ بصری | حفظ کردن | توانایی عددی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فراوانی تصمیم‌گیری | داخل ساختمان, با کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | صرف زمان به صورت نشسته | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره به چهره با افراد و در تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | میزان خودکارسازی | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
+          <t>فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | میزان خودکارسازی | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | بازرسان هوانوردی | تکنسین‌های اویونیک | رانندگان اتوبوس، درون‌شهری و بین‌شهری | خلبانان تجاری | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | مهمانداران هواپیما | رانندگان لوکوموتیو | توزیع‌کنندگان و دیسپچرهای برق | پاسخگویان تلفنی ایمنی عمومی | ترمزبانان، ماموران سیگنال و سوزنبانان راه‌آهن و کمک‌رانندگان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | اپراتورهای مترو و تراموا | تکنسین‌های ترافیک | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>سرپرستان جابجایی بار هواپیما | متصدیان خدمات هواپیما | متخصصان عملیات فرودگاه | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | بازرسان هوانوردی | تکنسین‌های هوانوردی | رانندگان اتوبوس، ترانزیت و بین‌شهری | خلبانان تجاری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | مهمانداران هواپیما | مهندسان لوکوموتیو | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای مخابراتی امنیت عمومی | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | رانندگان مترو و تراموا | تکنسین‌های ترافیک | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | نرم‌افزار سیستم پایش نویز هواپیما | Apache HTTP Server | Decision Support Technologies Propworks | زبان نشانه‌گذاری قابل گسترش XML | FileMaker Pro | سیستم مدیریت حمل و نقل زمینی | سیستم‌های تلویزیون پروتکل اینترنت | Intuit QuickBooks | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | نرم‌افزار برنامه‌ریزی عملیات | Oracle Database | سیستم کنترل درآمد دسترسی به پارکینگ | نرم‌افزار SAP | TRMI Airport AVI</t>
+          <t>Adobe Photoshop | نرم‌افزار سیستم پایش نویز هواپیما | Apache HTTP Server | Decision Support Technologies Propworks | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | سیستم مدیریت حمل و نقل زمینی | سیستم‌های تلویزیون پروتکل اینترنت | Intuit QuickBooks | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | نرم‌افزار برنامه‌ریزی عملیات | Oracle Database | سیستم کنترل درآمد دسترسی به پارکینگ | نرم‌افزار SAP | TRMI Airport AVI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>پایش | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | خدمات مشتریان و شخصی | آموزش و تربیت | مخابرات | مدیریت و امور اداری | قانون و دولت | اداری | کامپیوتر و الکترونیک | ریاضیات | ارتباطات و رسانه</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | مخابرات | مدیریت و اداره | قانون و دولت | اداری | رایانه و الکترونیک | ریاضیات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | دید نزدیک | دید دور | بیان کتبی | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | تقسیم توجه | تجسم فضایی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | بینایی نزدیک | بینایی دور | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | تقسیم توجه | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | مکالمات تلفنی | گفتگوهای چهره به چهره با افراد و در تیم‌ها | آزادی در تصمیم‌گیری | پیامد خطا | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارگران | خارج از ساختمان، در معرض تمام شرایط آب و هوایی | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | داخل ساختمان، با کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارگران | نزدیکی فیزیکی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | موقعیت‌های تعارض | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متصدیان خدمات هواپیما | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | بازرسان هوانوردی | خلبانان تجاری | دیسپچرهایی به جز پلیس، آتش‌نشانی و آمبولانس | مدیران تاسیسات | سرپرستان خط اول کارگران آتش‌نشانی و پیشگیری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارکنان امنیتی | مهمانداران هواپیما | رانندگان لوکوموتیو | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | مهندسان کشتی | تکنسین‌های ترافیک | بازرسان حمل و نقل | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متصدیان خدمات هواپیما | خلبانان، کمک‌خلبانان و مهندسان پرواز خطوط هوایی | بازرسان هوانوردی | خلبانان تجاری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران تسهیلات | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارکنان امنیتی | مهمانداران هواپیما | مهندسان لوکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | مهندسان کشتی | تکنسین‌های ترافیک | بازرسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0095_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0095_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | نظارت | استراتژی‌های یادگیری | درک مطلب | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | حمل‌ونقل | زبان انگلیسی | مدیریت و امور اداری | امور اداری | پرسنلی و منابع انسانی | ریاضیات | آموزش و تدریس | رایانه و الکترونیک | مخابرات | تولید و فرآوری | جغرافیا</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | مخابرات | تولید و فرآوری | جغرافیا</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید دور | استدلال قیاسی | دید نزدیک | هماهنگی چنداندامی | توجه انتخابی | سرعت ادراک | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری بستار | وضوح گفتار | تجسم فضایی | تقسیم زمان | قدرت ایستا | توجه شنیداری | توان بالاتنه | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | روانی ایده‌ها | ثبات دست و بازو | سرعت بستار | زمان واکنش | کنترل نرخ حرکت | چابکی دستی | ادراک عمق | انعطاف‌پذیری دامنه حرکتی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی دور | استدلال قیاسی | بینایی نزدیک | هماهنگی چند عضو | توجه انتخابی | سرعت ادراکی | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | وضوح گفتار | تجسم | تقسیم توجه | قدرت ایستا | توجه شنیداری | قدرت تنه | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | درک کتبی | روانی ایده‌ها | ثبات دست و بازو | سرعت بستار | زمان عکس‌العمل | کنترل نرخ | مهارت دستی | درک عمق | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | مأموران خدمات فرودگاهی و هواپیما | کارشناسان عملیات فرودگاهی | کارگزاران باربری و حمل بار | خلبانان تجاری | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارگران تولید و عملیات | متصدیان فورواردری و ترابری بار | رانندگان لیفتراک و تراکتورهای صنعتی | کارگران باربری، انبارداری و جابه‌جایی دستی کالا | رئیس قطار و سرپرستان توقفگاه‌های ریلی | کارگران بارگیری واگن‌های مخزن‌دار، کامیون و شناورها | بازرسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کنترلرهای ترافیک هوایی | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | کارشناسان عملیات فرودگاهی | کارگزاران حمل‌ونقل و بار | خلبانان تجاری | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده اول کارگران تولید و عملیات | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان ترابری و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand</t>
+          <t>سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار (First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | تفکر انتقادی | درک مطلب | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری | مدیریت و امور اداری | مکانیک | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | مدیریت و اداره | مکانیک | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | توجه انتخابی | مرتب‌سازی اطلاعات | بیان کتبی | دید دور | چابکی دستی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان کتبی | بینایی دور | مهارت دستی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارکنان سرگرمی و تفریحی به‌جز خدمات قمار | سرپرستان رده‌اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارکنان خدمات نظافتی و خدماتی | سرپرستان رده‌اول کارگران محوطه‌سازی و باغبانی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیاتی | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان برنامه‌ریزی، تولید و تسریع فرآیندها | کارشناسان هماهنگی بازیافت | مونتاژکاران تیمی</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | هماهنگ‌کنندگان امور بازیافت | مونتاژکاران گروهی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recycling Coordinators</t>
+          <t>هماهنگ‌کنندگان امور بازیافت (Recycling Coordinators)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری | آموزش و تدریس | تولید و فرآوری | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | رایانه و الکترونیک | حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | اداری | آموزش و پرورش | تولید و فرآوری | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | درک کتبی | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | بیان کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | درک کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بیان کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران امور عمومی و تاسیسات | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول کارکنان خدمات نظافتی و خدماتی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول کارگران تولید و عملیات | مدیران کل و مدیران عملیاتی | کارگران پاکسازی و امحای پسماندهای خطرناک | مدیران تولید صنعتی | کارشناسان لجستیک و زنجیره تأمین | تحلیل‌گران مدیریت و بهبود فرآیندها | کارشناسان برنامه‌ریزی، تولید و تسریع فرآیندها | کارشناسان مدیریت پروژه | کارگران بازیافت و بازیافت مواد | جمع‌آوری‌کنندگان زباله و مواد بازیافتی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده اول کارگران تولید و عملیات | مدیران کل و مدیران عملیات | کارگران امحا و پاک‌سازی مواد خطرناک | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه | کارگران بازیافت و تفکیک پسماند | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First-Line Supervisors of Material-Moving Machine and Vehicle Operators</t>
+          <t>سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار (First-Line Supervisors of Material-Moving Machine and Vehicle Operators)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | زبان انگلیسی | تولید و فرآوری | پرسنلی و منابع انسانی | ایمنی و امنیت عمومی | رایانه و الکترونیک | حمل‌ونقل | امور اداری | روانشناسی | آموزش و تدریس | حقوق و مقررات دولتی | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | زبان انگلیسی | تولید و فرآوری | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | رایانه و الکترونیک | حمل و نقل | اداری | روان‌شناسی | آموزش و پرورش | قانون و دولت | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | دید نزدیک | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | دید دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری طبقه‌بندی | مهارت کار با اعداد | نوآوری | روانی ایده‌ها | تقسیم زمان</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | بینایی دور | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توانایی عددی | اصالت | روانی ایده‌ها | تقسیم توجه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارکنان سرگرمی و تفریحی به‌جز خدمات قمار | سرپرستان رده‌اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول کارکنان خدمات نظافتی و خدماتی | سرپرستان رده‌اول کارگران محوطه‌سازی و باغبانی | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیاتی | مدیران تولید صنعتی | رئیس قطار و سرپرستان توقفگاه‌های ریلی | کارشناسان هماهنگی بازیافت | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | مدیران تولید صنعتی | رؤسای قطار و مدیران محوطه راه‌آهن | هماهنگ‌کنندگان امور بازیافت | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First-Line Supervisors of Passenger Attendants</t>
+          <t>سرپرستان رده‌اول مهمانداران و خدمه مسافری (First-Line Supervisors of Passenger Attendants)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنلی و منابع انسانی | آموزش و تدریس | جغرافیا</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | مدیریت و اداره | ایمنی و امنیت عمومی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تقسیم زمان | چابکی انگشتان | چابکی دستی | دید دور | توانایی حفظ و یادآوری | روانی ایده‌ها | بیان کتبی | نوآوری</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارکنان سرگرمی و تفریحی به‌جز خدمات قمار | سرپرستان رده‌اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان رده‌اول کارگران آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول کارکنان خدمات نظافتی و خدماتی | سرپرستان رده‌اول کارگران محوطه‌سازی و باغبانی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول کارکنان خدمات فردی | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیاتی | کارشناسان منابع انسانی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | کارشناسان منابع انسانی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First-Line Supervisors of Transportation Workers, All Other</t>
+          <t>سرپرستان رده‌اول سایر کارکنان ترابری و حمل‌ونقل (First-Line Supervisors of Transportation Workers, All Other)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و امور اداری | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | پرسنلی و منابع انسانی | آموزش و تدریس | حقوق و مقررات دولتی | رایانه و الکترونیک</t>
+          <t>حمل و نقل | مدیریت و اداره | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | قانون و دولت | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | نوآوری | توجه انتخابی | تقسیم زمان | تجسم فضایی | توانایی حفظ و یادآوری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان هماهنگی بازیافت | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و زنجیره تأمین | تحلیل‌گران لجستیک | مدیران زنجیره تأمین | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | کارگزاران باربری و حمل بار | متصدیان فورواردری و ترابری بار | بازرسان حمل‌ونقل | کارشناسان عملیات فرودگاهی | رانندگان کامیون‌های سنگین و تریلی | رانندگان اتوبوس درون‌شهری و برون‌شهری | رئیس قطار و سرپرستان توقفگاه‌های ریلی | مدیران کل و مدیران عملیاتی | کارشناسان برنامه‌ریزی، تولید و تسریع فرآیندها | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
+          <t>سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان بارگیری و جابه‌جایی بار هواپیما | هماهنگ‌کنندگان امور بازیافت | مدیران حمل‌ونقل، انبارداری و توزیع | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مدیران زنجیره تامین | متصدیان دیسپاچ و اعزام | کارگزاران حمل‌ونقل و بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | بازرسان ترابری و حمل‌ونقل | کارشناسان عملیات فرودگاهی | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | رؤسای قطار و مدیران محوطه راه‌آهن | مدیران کل و مدیران عملیات | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Airline Pilots, Copilots, and Flight Engineers</t>
+          <t>خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز (Airline Pilots, Copilots, and Flight Engineers)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | زبان انگلیسی | ایمنی و امنیت عمومی | جغرافیا | مکانیک | ریاضیات | رایانه و الکترونیک | فیزیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | جغرافیا | مکانیک | ریاضیات | رایانه و الکترونیک | فیزیک | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>جهت‌یابی پاسخ | حساسیت به مسئله | دقت کنترل حرکتی | دید دور | دید نزدیک | زمان واکنش | کنترل نرخ حرکت | ادراک عمق | استدلال قیاسی | سرعت ادراک | انعطاف‌پذیری بستار | جهت‌یابی فضایی | توجه انتخابی | تقسیم زمان | ثبات دست و بازو | هماهنگی چنداندامی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید محیطی | وضوح گفتار | حساسیت شنوایی | تشخیص گفتار | تمایز رنگ‌ها | حساسیت به تابش خیره‌کننده | چابکی دستی | تجسم فضایی | سرعت بستار | دید در شب | مهارت کار با اعداد | توجه شنیداری | چابکی انگشتان | توانایی حفظ و یادآوری | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها</t>
+          <t>جهت‌گیری پاسخ | حساسیت به مسئله | دقت کنترل | بینایی دور | بینایی نزدیک | زمان عکس‌العمل | کنترل نرخ | درک عمق | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری بستار | جهت‌گیری فضایی | توجه انتخابی | تقسیم توجه | ثبات دست و بازو | هماهنگی چند عضو | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی محیطی | وضوح گفتار | حساسیت شنوایی | تشخیص گفتار | تشخیص رنگ بصری | حساسیت به درخشندگی شدید | مهارت دستی | تجسم | سرعت بستار | بینایی در شب | توانایی عددی | توجه شنیداری | مهارت انگشتان | حفظ کردن | استدلال ریاضی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های مهندسی هوافضا و عملیات پرواز | مهندسان هوافضا | کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | مکانیک‌ها و تکنسین‌های فنی هواپیما | مأموران خدمات فرودگاهی و هواپیما | کارشناسان عملیات فرودگاهی | بازرسان استاندارد پرواز و ایمنی هوانوردی | تکنسین‌های اویونیک و الکترونیک پرواز | کاپیتان‌ها، افسران اول و ناوبانان شناورها | خلبانان تجاری | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | لکوموتیورانان | هدایت‌کنندگان قایق‌های موتوری | متصدیان ترمز، علائم، سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رئیس قطار و سرپرستان توقفگاه‌های ریلی | ملوانان و نیروهای فنی موتورخانه شناور | مهندسان موتورخانه شناورهای دریایی | بازرسان حمل‌ونقل</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | مکانیک و تکنسین خدمات هواپیما | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | کارشناسان عملیات فرودگاهی | بازرسان هوانوردی و فرودگاهی | تکنسین‌های اویونیک و الکترونیک پرواز | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | خلبانان تجاری | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | لکوموتیورانان | قایقرانان قایق‌های موتوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Commercial Pilots</t>
+          <t>خلبانان تجاری (Commercial Pilots)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش عملیات | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | حمل‌ونقل | جغرافیا | ایمنی و امنیت عمومی | مکانیک | حقوق و مقررات دولتی | رایانه و الکترونیک | فیزیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | رایانه و الکترونیک | فیزیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | سرعت ادراک | دقت کنترل حرکتی | دید نزدیک | جهت‌یابی پاسخ | زمان واکنش | دید دور | ادراک عمق | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | هماهنگی چنداندامی | کنترل نرخ حرکت | جهت‌یابی فضایی | درک کتبی | تشخیص گفتار | وضوح گفتار | تقسیم زمان | انعطاف‌پذیری بستار | چابکی دستی | بیان کتبی | ثبات دست و بازو | تجسم فضایی | توجه شنیداری | حساسیت شنوایی | حساسیت به تابش خیره‌کننده | سرعت بستار | انعطاف‌پذیری طبقه‌بندی | نوآوری | روانی ایده‌ها | دید محیطی | تمایز رنگ‌ها</t>
+          <t>حساسیت به مسئله | سرعت ادراکی | دقت کنترل | بینایی نزدیک | جهت‌گیری پاسخ | زمان عکس‌العمل | بینایی دور | درک عمق | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | کنترل نرخ | جهت‌گیری فضایی | درک کتبی | تشخیص گفتار | وضوح گفتار | تقسیم توجه | انعطاف‌پذیری بستار | مهارت دستی | بیان کتبی | ثبات دست و بازو | تجسم | توجه شنیداری | حساسیت شنوایی | حساسیت به درخشندگی شدید | سرعت بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | بینایی محیطی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های مهندسی هوافضا و عملیات پرواز | کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | مکانیک‌ها و تکنسین‌های فنی هواپیما | مأموران خدمات فرودگاهی و هواپیما | کارشناسان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | بازرسان استاندارد پرواز و ایمنی هوانوردی | تکنسین‌های اویونیک و الکترونیک پرواز | تصویربرداران تلویزیون، ویدئو و سینما | کاپیتان‌ها، افسران اول و ناوبانان شناورها | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | مهمانداران هواپیما | رانندگان کامیون‌های سنگین و تریلی | لکوموتیورانان | مهندسان محوطه ریلی و لکوموتیورانان مانور | رئیس قطار و سرپرستان توقفگاه‌های ریلی | تکنسین‌های سنجش از دور | مهندسان موتورخانه شناورهای دریایی | بازرسان حمل‌ونقل</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | مکانیک و تکنسین خدمات هواپیما | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | کارشناسان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | بازرسان هوانوردی و فرودگاهی | تکنسین‌های اویونیک و الکترونیک پرواز | تصویربرداران تلویزیون، ویدیو و سینما | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | متصدیان دیسپاچ و اعزام | مهمانداران هواپیما | رانندگان خودروهای سنگین و کشنده‌ها | لکوموتیورانان | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | رؤسای قطار و مدیران محوطه راه‌آهن | تکنسین‌های سنجش از دور | مهندسان فنی کشتی | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Air Traffic Controllers</t>
+          <t>کنترلرهای ترافیک هوایی (Air Traffic Controllers)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | جغرافیا | مخابرات | ریاضیات</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | آموزش و پرورش | خدمات مشتری و شخصی | جغرافیا | مخابرات | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | استدلال قیاسی | انعطاف‌پذیری بستار | سرعت بستار | استدلال استقرایی | سرعت ادراک | تقسیم زمان | دید نزدیک | دید دور | وضوح گفتار | مرتب‌سازی اطلاعات | تشخیص گفتار | درک کتبی | انعطاف‌پذیری طبقه‌بندی | توجه شنیداری | تجسم فضایی | نوآوری | روانی ایده‌ها | بیان کتبی | استدلال ریاضی | تمایز رنگ‌ها | توانایی حفظ و یادآوری | مهارت کار با اعداد</t>
+          <t>حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | استدلال قیاسی | انعطاف‌پذیری بستار | سرعت بستار | استدلال استقرایی | سرعت ادراکی | تقسیم توجه | بینایی نزدیک | بینایی دور | وضوح گفتار | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک کتبی | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | تجسم | اصالت | روانی ایده‌ها | بیان کتبی | استدلال ریاضی | تشخیص رنگ بصری | حفظ کردن | توانایی عددی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | مأموران خدمات فرودگاهی و هواپیما | کارشناسان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | بازرسان استاندارد پرواز و ایمنی هوانوردی | تکنسین‌های اویونیک و الکترونیک پرواز | رانندگان اتوبوس درون‌شهری و برون‌شهری | خلبانان تجاری | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | لکوموتیورانان | توزیع‌کنندگان و دیسپچرهای شبکه برق | متصدیان ارتباطات رادیویی و دیسپچ فوریت‌ها | متصدیان ترمز، علائم، سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رئیس قطار و سرپرستان توقفگاه‌های ریلی | رانندگان قطار شهری و تراموا | تکنسین‌های فنی ترافیک و مهندسی ترافیک | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | کارشناسان عملیات فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | بازرسان هوانوردی و فرودگاهی | تکنسین‌های اویونیک و الکترونیک پرواز | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | خلبانان تجاری | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | لکوموتیورانان | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای فوریت‌های پلیسی و امدادی | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | رانندگان مترو و تراموا | تکنسین‌های ترافیک | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Airfield Operations Specialists</t>
+          <t>کارشناسان عملیات فرودگاهی (Airfield Operations Specialists)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | زبان انگلیسی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | مخابرات | مدیریت و امور اداری | حقوق و مقررات دولتی | امور اداری | رایانه و الکترونیک | ریاضیات | ارتباطات و رسانه</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | خدمات مشتری و شخصی | آموزش و پرورش | مخابرات | مدیریت و اداره | قانون و دولت | اداری | رایانه و الکترونیک | ریاضیات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | دید نزدیک | دید دور | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری بستار | سرعت ادراک | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | توجه شنیداری | تقسیم زمان | تجسم فضایی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | استدلال استقرایی | بینایی نزدیک | بینایی دور | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | سرعت ادراکی | توجه انتخابی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | تقسیم توجه | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | مأموران خدمات فرودگاهی و هواپیما | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | بازرسان استاندارد پرواز و ایمنی هوانوردی | خلبانان تجاری | متصدیان دیسپچ به‌جز پلیس، آتش‌نشانی و اورژانس | مدیران امور عمومی و تاسیسات | سرپرستان رده‌اول نیروهای آتش‌نشانی و خدمات ایمنی | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و ناوگان حمل بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان حراست و انتظامات | مهمانداران هواپیما | لکوموتیورانان | رئیس قطار و سرپرستان توقفگاه‌های ریلی | مهندسان موتورخانه شناورهای دریایی | تکنسین‌های فنی ترافیک و مهندسی ترافیک | بازرسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | خلبانان خطوط هوایی، کمک‌خلبانان و مهندسان پرواز | بازرسان هوانوردی و فرودگاهی | خلبانان تجاری | متصدیان دیسپاچ و اعزام | مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان حراست و انتظامات | مهمانداران هواپیما | لکوموتیورانان | رؤسای قطار و مدیران محوطه راه‌آهن | مهندسان فنی کشتی | تکنسین‌های ترافیک | بازرسان ترابری و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
